--- a/Finances.xlsx
+++ b/Finances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\aleks\Рабочий стол\DEV\python\Excel-table-parser\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36913D53-B479-4BAA-8B2B-0D38BD0B1DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84D514A-1204-427B-B378-24FAA5BC3353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="794" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="794" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Расходы" sheetId="2" r:id="rId1"/>
@@ -583,9 +583,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0\ &quot;₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0\ &quot;₽&quot;"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -2127,28 +2127,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="10" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2257,33 +2257,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2306,56 +2339,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2719,44 +2708,44 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12"/>
-      <c r="B1" s="154">
+      <c r="B1" s="161">
         <v>2025</v>
       </c>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="155"/>
-      <c r="S1" s="155"/>
-      <c r="T1" s="155"/>
-      <c r="U1" s="155"/>
-      <c r="V1" s="155"/>
-      <c r="W1" s="155"/>
-      <c r="X1" s="155"/>
-      <c r="Y1" s="155"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="155"/>
-      <c r="AB1" s="155"/>
-      <c r="AC1" s="155"/>
-      <c r="AD1" s="155"/>
-      <c r="AE1" s="155"/>
-      <c r="AF1" s="155"/>
-      <c r="AG1" s="155"/>
-      <c r="AH1" s="155"/>
-      <c r="AI1" s="155"/>
-      <c r="AJ1" s="155"/>
-      <c r="AK1" s="155"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
+      <c r="L1" s="162"/>
+      <c r="M1" s="162"/>
+      <c r="N1" s="162"/>
+      <c r="O1" s="162"/>
+      <c r="P1" s="162"/>
+      <c r="Q1" s="162"/>
+      <c r="R1" s="162"/>
+      <c r="S1" s="162"/>
+      <c r="T1" s="162"/>
+      <c r="U1" s="162"/>
+      <c r="V1" s="162"/>
+      <c r="W1" s="162"/>
+      <c r="X1" s="162"/>
+      <c r="Y1" s="162"/>
+      <c r="Z1" s="162"/>
+      <c r="AA1" s="162"/>
+      <c r="AB1" s="162"/>
+      <c r="AC1" s="162"/>
+      <c r="AD1" s="162"/>
+      <c r="AE1" s="162"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="162"/>
+      <c r="AH1" s="162"/>
+      <c r="AI1" s="162"/>
+      <c r="AJ1" s="162"/>
+      <c r="AK1" s="162"/>
       <c r="AL1" s="95"/>
       <c r="AM1" s="17"/>
     </row>
@@ -3517,7 +3506,7 @@
       <c r="AM11" s="13"/>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A12" s="179" t="s">
+      <c r="A12" s="166" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="24"/>
@@ -3560,7 +3549,7 @@
       <c r="AM12" s="13"/>
     </row>
     <row r="13" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="180"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="30"/>
       <c r="C13" s="28"/>
       <c r="D13" s="20"/>
@@ -3726,44 +3715,44 @@
     </row>
     <row r="19" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="41"/>
-      <c r="B19" s="157">
+      <c r="B19" s="163">
         <v>2024</v>
       </c>
-      <c r="C19" s="158"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="158"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
-      <c r="J19" s="158"/>
-      <c r="K19" s="158"/>
-      <c r="L19" s="158"/>
-      <c r="M19" s="158"/>
-      <c r="N19" s="158"/>
-      <c r="O19" s="158"/>
-      <c r="P19" s="158"/>
-      <c r="Q19" s="158"/>
-      <c r="R19" s="158"/>
-      <c r="S19" s="158"/>
-      <c r="T19" s="158"/>
-      <c r="U19" s="158"/>
-      <c r="V19" s="158"/>
-      <c r="W19" s="158"/>
-      <c r="X19" s="158"/>
-      <c r="Y19" s="158"/>
-      <c r="Z19" s="158"/>
-      <c r="AA19" s="158"/>
-      <c r="AB19" s="158"/>
-      <c r="AC19" s="158"/>
-      <c r="AD19" s="158"/>
-      <c r="AE19" s="158"/>
-      <c r="AF19" s="158"/>
-      <c r="AG19" s="158"/>
-      <c r="AH19" s="158"/>
-      <c r="AI19" s="158"/>
-      <c r="AJ19" s="158"/>
-      <c r="AK19" s="159"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="164"/>
+      <c r="H19" s="164"/>
+      <c r="I19" s="164"/>
+      <c r="J19" s="164"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="164"/>
+      <c r="M19" s="164"/>
+      <c r="N19" s="164"/>
+      <c r="O19" s="164"/>
+      <c r="P19" s="164"/>
+      <c r="Q19" s="164"/>
+      <c r="R19" s="164"/>
+      <c r="S19" s="164"/>
+      <c r="T19" s="164"/>
+      <c r="U19" s="164"/>
+      <c r="V19" s="164"/>
+      <c r="W19" s="164"/>
+      <c r="X19" s="164"/>
+      <c r="Y19" s="164"/>
+      <c r="Z19" s="164"/>
+      <c r="AA19" s="164"/>
+      <c r="AB19" s="164"/>
+      <c r="AC19" s="164"/>
+      <c r="AD19" s="164"/>
+      <c r="AE19" s="164"/>
+      <c r="AF19" s="164"/>
+      <c r="AG19" s="164"/>
+      <c r="AH19" s="164"/>
+      <c r="AI19" s="164"/>
+      <c r="AJ19" s="164"/>
+      <c r="AK19" s="165"/>
       <c r="AL19" s="127"/>
       <c r="AM19" s="17"/>
     </row>
@@ -4526,7 +4515,7 @@
       <c r="AM29" s="13"/>
     </row>
     <row r="30" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="179" t="s">
+      <c r="A30" s="166" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="24"/>
@@ -4569,7 +4558,7 @@
       <c r="AM30" s="13"/>
     </row>
     <row r="31" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="180"/>
+      <c r="A31" s="167"/>
       <c r="B31" s="30"/>
       <c r="C31" s="28"/>
       <c r="D31" s="20"/>
@@ -4783,34 +4772,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="182"/>
-      <c r="B1" s="160">
+      <c r="A1" s="153"/>
+      <c r="B1" s="170">
         <v>2025</v>
       </c>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="155"/>
-      <c r="S1" s="155"/>
-      <c r="T1" s="155"/>
-      <c r="U1" s="155"/>
-      <c r="V1" s="155"/>
-      <c r="W1" s="155"/>
-      <c r="X1" s="155"/>
-      <c r="Y1" s="155"/>
-      <c r="Z1" s="161"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
+      <c r="L1" s="162"/>
+      <c r="M1" s="162"/>
+      <c r="N1" s="162"/>
+      <c r="O1" s="162"/>
+      <c r="P1" s="162"/>
+      <c r="Q1" s="162"/>
+      <c r="R1" s="162"/>
+      <c r="S1" s="162"/>
+      <c r="T1" s="162"/>
+      <c r="U1" s="162"/>
+      <c r="V1" s="162"/>
+      <c r="W1" s="162"/>
+      <c r="X1" s="162"/>
+      <c r="Y1" s="162"/>
+      <c r="Z1" s="171"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="109"/>
@@ -5174,7 +5163,7 @@
       <c r="Z7" s="19"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="162" t="s">
+      <c r="A8" s="168" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="24"/>
@@ -5204,7 +5193,7 @@
       <c r="Z8" s="18"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="156"/>
+      <c r="A9" s="169"/>
       <c r="B9" s="25"/>
       <c r="C9" s="19"/>
       <c r="D9" s="25"/>
@@ -5301,62 +5290,62 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="181"/>
-      <c r="B12" s="181"/>
-      <c r="C12" s="181"/>
-      <c r="D12" s="181"/>
-      <c r="E12" s="181"/>
-      <c r="F12" s="181"/>
-      <c r="G12" s="181"/>
-      <c r="H12" s="181"/>
-      <c r="I12" s="181"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="181"/>
-      <c r="L12" s="181"/>
-      <c r="M12" s="181"/>
-      <c r="N12" s="181"/>
-      <c r="O12" s="181"/>
-      <c r="P12" s="181"/>
-      <c r="Q12" s="181"/>
-      <c r="R12" s="181"/>
-      <c r="S12" s="181"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="181"/>
-      <c r="V12" s="181"/>
-      <c r="W12" s="181"/>
-      <c r="X12" s="181"/>
-      <c r="Y12" s="181"/>
-      <c r="Z12" s="181"/>
+      <c r="A12" s="152"/>
+      <c r="B12" s="152"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="152"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="152"/>
+      <c r="L12" s="152"/>
+      <c r="M12" s="152"/>
+      <c r="N12" s="152"/>
+      <c r="O12" s="152"/>
+      <c r="P12" s="152"/>
+      <c r="Q12" s="152"/>
+      <c r="R12" s="152"/>
+      <c r="S12" s="152"/>
+      <c r="T12" s="152"/>
+      <c r="U12" s="152"/>
+      <c r="V12" s="152"/>
+      <c r="W12" s="152"/>
+      <c r="X12" s="152"/>
+      <c r="Y12" s="152"/>
+      <c r="Z12" s="152"/>
     </row>
     <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="108"/>
-      <c r="B13" s="160">
+      <c r="B13" s="170">
         <v>2024</v>
       </c>
-      <c r="C13" s="155"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="155"/>
-      <c r="F13" s="155"/>
-      <c r="G13" s="155"/>
-      <c r="H13" s="155"/>
-      <c r="I13" s="155"/>
-      <c r="J13" s="155"/>
-      <c r="K13" s="155"/>
-      <c r="L13" s="155"/>
-      <c r="M13" s="155"/>
-      <c r="N13" s="155"/>
-      <c r="O13" s="155"/>
-      <c r="P13" s="155"/>
-      <c r="Q13" s="155"/>
-      <c r="R13" s="155"/>
-      <c r="S13" s="155"/>
-      <c r="T13" s="155"/>
-      <c r="U13" s="155"/>
-      <c r="V13" s="155"/>
-      <c r="W13" s="155"/>
-      <c r="X13" s="155"/>
-      <c r="Y13" s="155"/>
-      <c r="Z13" s="161"/>
+      <c r="C13" s="162"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="162"/>
+      <c r="K13" s="162"/>
+      <c r="L13" s="162"/>
+      <c r="M13" s="162"/>
+      <c r="N13" s="162"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="162"/>
+      <c r="Q13" s="162"/>
+      <c r="R13" s="162"/>
+      <c r="S13" s="162"/>
+      <c r="T13" s="162"/>
+      <c r="U13" s="162"/>
+      <c r="V13" s="162"/>
+      <c r="W13" s="162"/>
+      <c r="X13" s="162"/>
+      <c r="Y13" s="162"/>
+      <c r="Z13" s="171"/>
     </row>
     <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="109"/>
@@ -5720,7 +5709,7 @@
       <c r="Z19" s="19"/>
     </row>
     <row r="20" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="162" t="s">
+      <c r="A20" s="168" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="24"/>
@@ -5750,7 +5739,7 @@
       <c r="Z20" s="18"/>
     </row>
     <row r="21" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="156"/>
+      <c r="A21" s="169"/>
       <c r="B21" s="25"/>
       <c r="C21" s="19"/>
       <c r="D21" s="25"/>
@@ -5889,19 +5878,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="185" t="s">
+      <c r="B1" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="184" t="s">
+      <c r="C1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="184" t="s">
+      <c r="D1" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="183" t="s">
+      <c r="E1" s="154" t="s">
         <v>123</v>
       </c>
       <c r="F1" s="151" t="s">
@@ -5941,28 +5930,28 @@
       <c r="O3" s="148"/>
     </row>
     <row r="4" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163">
+      <c r="A4" s="172">
         <v>2025</v>
       </c>
       <c r="B4" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="186">
+      <c r="C4" s="157">
         <v>10000</v>
       </c>
-      <c r="D4" s="186">
+      <c r="D4" s="157">
         <f>SUM(C4:$C$31)</f>
         <v>110500</v>
       </c>
-      <c r="E4" s="186">
+      <c r="E4" s="157">
         <v>112073</v>
       </c>
       <c r="F4" s="147">
-        <f t="shared" ref="F3:F30" si="0">IF((E4)/(E5+C4)&lt;1,(1-(E4)/(E5+C4))*(-1),(E4)/(E5+C4)-1)</f>
+        <f t="shared" ref="F4:F27" si="0">IF((E4)/(E5+C4)&lt;1,(1-(E4)/(E5+C4))*(-1),(E4)/(E5+C4)-1)</f>
         <v>7.5154849555454373E-3</v>
       </c>
       <c r="G4" s="129">
-        <f t="shared" ref="G3:G30" si="1">IF(E4/D4&lt;1,(1-E4/D4)*(-1),E4/D4-1)</f>
+        <f t="shared" ref="G4:G27" si="1">IF(E4/D4&lt;1,(1-E4/D4)*(-1),E4/D4-1)</f>
         <v>1.4235294117647124E-2</v>
       </c>
       <c r="H4" s="148"/>
@@ -5975,18 +5964,18 @@
       <c r="O4" s="148"/>
     </row>
     <row r="5" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="152"/>
+      <c r="A5" s="173"/>
       <c r="B5" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="186">
+      <c r="C5" s="157">
         <v>10000</v>
       </c>
-      <c r="D5" s="186">
+      <c r="D5" s="157">
         <f>SUM(C5:$C$31)</f>
         <v>100500</v>
       </c>
-      <c r="E5" s="186">
+      <c r="E5" s="157">
         <v>101237</v>
       </c>
       <c r="F5" s="147">
@@ -6007,18 +5996,18 @@
       <c r="O5" s="148"/>
     </row>
     <row r="6" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="152"/>
+      <c r="A6" s="173"/>
       <c r="B6" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="186">
+      <c r="C6" s="157">
         <v>10000</v>
       </c>
-      <c r="D6" s="186">
+      <c r="D6" s="157">
         <f>SUM(C6:$C$31)</f>
         <v>90500</v>
       </c>
-      <c r="E6" s="186">
+      <c r="E6" s="157">
         <v>91837</v>
       </c>
       <c r="F6" s="147">
@@ -6039,18 +6028,18 @@
       <c r="O6" s="148"/>
     </row>
     <row r="7" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="152"/>
+      <c r="A7" s="173"/>
       <c r="B7" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="186">
+      <c r="C7" s="157">
         <v>10000</v>
       </c>
-      <c r="D7" s="186">
+      <c r="D7" s="157">
         <f>SUM(C7:$C$31)</f>
         <v>80500</v>
       </c>
-      <c r="E7" s="186">
+      <c r="E7" s="157">
         <v>80408</v>
       </c>
       <c r="F7" s="147">
@@ -6071,18 +6060,18 @@
       <c r="O7" s="148"/>
     </row>
     <row r="8" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="152"/>
+      <c r="A8" s="173"/>
       <c r="B8" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="186">
+      <c r="C8" s="157">
         <v>10000</v>
       </c>
-      <c r="D8" s="186">
+      <c r="D8" s="157">
         <f>SUM(C8:$C$31)</f>
         <v>70500</v>
       </c>
-      <c r="E8" s="186">
+      <c r="E8" s="157">
         <v>69127</v>
       </c>
       <c r="F8" s="147">
@@ -6103,18 +6092,18 @@
       <c r="O8" s="148"/>
     </row>
     <row r="9" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="152"/>
+      <c r="A9" s="173"/>
       <c r="B9" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="186">
+      <c r="C9" s="157">
         <v>5000</v>
       </c>
-      <c r="D9" s="186">
+      <c r="D9" s="157">
         <f>SUM(C9:$C$31)</f>
         <v>60500</v>
       </c>
-      <c r="E9" s="186">
+      <c r="E9" s="157">
         <v>59271</v>
       </c>
       <c r="F9" s="147">
@@ -6135,18 +6124,18 @@
       <c r="O9" s="148"/>
     </row>
     <row r="10" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="152"/>
+      <c r="A10" s="173"/>
       <c r="B10" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="186">
+      <c r="C10" s="157">
         <v>5000</v>
       </c>
-      <c r="D10" s="186">
+      <c r="D10" s="157">
         <f>SUM(C10:$C$31)</f>
         <v>55500</v>
       </c>
-      <c r="E10" s="186">
+      <c r="E10" s="157">
         <v>54927</v>
       </c>
       <c r="F10" s="147">
@@ -6167,18 +6156,18 @@
       <c r="O10" s="148"/>
     </row>
     <row r="11" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="152"/>
+      <c r="A11" s="173"/>
       <c r="B11" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="186">
+      <c r="C11" s="157">
         <v>5000</v>
       </c>
-      <c r="D11" s="186">
+      <c r="D11" s="157">
         <f>SUM(C11:$C$31)</f>
         <v>50500</v>
       </c>
-      <c r="E11" s="186">
+      <c r="E11" s="157">
         <v>49371</v>
       </c>
       <c r="F11" s="147">
@@ -6199,18 +6188,18 @@
       <c r="O11" s="148"/>
     </row>
     <row r="12" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="152"/>
+      <c r="A12" s="173"/>
       <c r="B12" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="186">
+      <c r="C12" s="157">
         <v>5000</v>
       </c>
-      <c r="D12" s="186">
+      <c r="D12" s="157">
         <f>SUM(C12:$C$31)</f>
         <v>45500</v>
       </c>
-      <c r="E12" s="186">
+      <c r="E12" s="157">
         <v>44381</v>
       </c>
       <c r="F12" s="147">
@@ -6231,18 +6220,18 @@
       <c r="O12" s="148"/>
     </row>
     <row r="13" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="152"/>
+      <c r="A13" s="173"/>
       <c r="B13" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="186">
+      <c r="C13" s="157">
         <v>7000</v>
       </c>
-      <c r="D13" s="186">
+      <c r="D13" s="157">
         <f>SUM(C13:$C$31)</f>
         <v>40500</v>
       </c>
-      <c r="E13" s="186">
+      <c r="E13" s="157">
         <v>41973</v>
       </c>
       <c r="F13" s="147">
@@ -6263,18 +6252,18 @@
       <c r="O13" s="148"/>
     </row>
     <row r="14" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="152"/>
+      <c r="A14" s="173"/>
       <c r="B14" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="186">
-        <v>0</v>
-      </c>
-      <c r="D14" s="186">
+      <c r="C14" s="157">
+        <v>0</v>
+      </c>
+      <c r="D14" s="157">
         <f>SUM(C14:$C$31)</f>
         <v>33500</v>
       </c>
-      <c r="E14" s="186">
+      <c r="E14" s="157">
         <v>34920</v>
       </c>
       <c r="F14" s="147">
@@ -6295,18 +6284,18 @@
       <c r="O14" s="148"/>
     </row>
     <row r="15" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="153"/>
+      <c r="A15" s="174"/>
       <c r="B15" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="186">
+      <c r="C15" s="157">
         <v>3500</v>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="157">
         <f>SUM(C15:$C$31)</f>
         <v>33500</v>
       </c>
-      <c r="E15" s="186">
+      <c r="E15" s="157">
         <v>33049</v>
       </c>
       <c r="F15" s="147">
@@ -6327,20 +6316,20 @@
       <c r="O15" s="148"/>
     </row>
     <row r="16" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="163">
+      <c r="A16" s="172">
         <v>2024</v>
       </c>
       <c r="B16" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="186">
+      <c r="C16" s="157">
         <v>3500</v>
       </c>
-      <c r="D16" s="186">
+      <c r="D16" s="157">
         <f>SUM(C16:$C$31)</f>
         <v>30000</v>
       </c>
-      <c r="E16" s="186">
+      <c r="E16" s="157">
         <v>29310</v>
       </c>
       <c r="F16" s="147">
@@ -6361,18 +6350,18 @@
       <c r="O16" s="148"/>
     </row>
     <row r="17" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="152"/>
+      <c r="A17" s="173"/>
       <c r="B17" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="186">
+      <c r="C17" s="157">
         <v>3500</v>
       </c>
-      <c r="D17" s="186">
+      <c r="D17" s="157">
         <f>SUM(C17:$C$31)</f>
         <v>26500</v>
       </c>
-      <c r="E17" s="186">
+      <c r="E17" s="157">
         <v>24976</v>
       </c>
       <c r="F17" s="147">
@@ -6393,18 +6382,18 @@
       <c r="O17" s="148"/>
     </row>
     <row r="18" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="152"/>
+      <c r="A18" s="173"/>
       <c r="B18" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="186">
+      <c r="C18" s="157">
         <v>2000</v>
       </c>
-      <c r="D18" s="186">
+      <c r="D18" s="157">
         <f>SUM(C18:$C$31)</f>
         <v>23000</v>
       </c>
-      <c r="E18" s="186">
+      <c r="E18" s="157">
         <v>22984</v>
       </c>
       <c r="F18" s="147">
@@ -6425,18 +6414,18 @@
       <c r="O18" s="148"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="152"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="186">
+      <c r="C19" s="157">
         <v>2000</v>
       </c>
-      <c r="D19" s="186">
+      <c r="D19" s="157">
         <f>SUM(C19:$C$31)</f>
         <v>21000</v>
       </c>
-      <c r="E19" s="187">
+      <c r="E19" s="158">
         <v>20345</v>
       </c>
       <c r="F19" s="147">
@@ -6457,18 +6446,18 @@
       <c r="O19" s="148"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="152"/>
+      <c r="A20" s="173"/>
       <c r="B20" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="186">
+      <c r="C20" s="157">
         <v>2000</v>
       </c>
-      <c r="D20" s="186">
+      <c r="D20" s="157">
         <f>SUM(C20:$C$31)</f>
         <v>19000</v>
       </c>
-      <c r="E20" s="187">
+      <c r="E20" s="158">
         <v>17623</v>
       </c>
       <c r="F20" s="147">
@@ -6489,18 +6478,18 @@
       <c r="O20" s="148"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="152"/>
+      <c r="A21" s="173"/>
       <c r="B21" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="186">
+      <c r="C21" s="157">
         <v>2000</v>
       </c>
-      <c r="D21" s="186">
+      <c r="D21" s="157">
         <f>SUM(C21:$C$31)</f>
         <v>17000</v>
       </c>
-      <c r="E21" s="187">
+      <c r="E21" s="158">
         <v>15987</v>
       </c>
       <c r="F21" s="147">
@@ -6521,18 +6510,18 @@
       <c r="O21" s="148"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="152"/>
+      <c r="A22" s="173"/>
       <c r="B22" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="186">
+      <c r="C22" s="157">
         <v>5000</v>
       </c>
-      <c r="D22" s="186">
+      <c r="D22" s="157">
         <f>SUM(C22:$C$31)</f>
         <v>15000</v>
       </c>
-      <c r="E22" s="187">
+      <c r="E22" s="158">
         <v>14732</v>
       </c>
       <c r="F22" s="147">
@@ -6553,18 +6542,18 @@
       <c r="O22" s="148"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="152"/>
+      <c r="A23" s="173"/>
       <c r="B23" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="186">
-        <v>0</v>
-      </c>
-      <c r="D23" s="186">
+      <c r="C23" s="157">
+        <v>0</v>
+      </c>
+      <c r="D23" s="157">
         <f>SUM(C23:$C$31)</f>
         <v>10000</v>
       </c>
-      <c r="E23" s="187">
+      <c r="E23" s="158">
         <v>9834</v>
       </c>
       <c r="F23" s="147">
@@ -6585,18 +6574,18 @@
       <c r="O23" s="148"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="152"/>
+      <c r="A24" s="173"/>
       <c r="B24" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="186">
-        <v>0</v>
-      </c>
-      <c r="D24" s="186">
+      <c r="C24" s="157">
+        <v>0</v>
+      </c>
+      <c r="D24" s="157">
         <f>SUM(C24:$C$31)</f>
         <v>10000</v>
       </c>
-      <c r="E24" s="187">
+      <c r="E24" s="158">
         <v>10670</v>
       </c>
       <c r="F24" s="147">
@@ -6617,18 +6606,18 @@
       <c r="O24" s="148"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="152"/>
+      <c r="A25" s="173"/>
       <c r="B25" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="186">
+      <c r="C25" s="157">
         <v>5000</v>
       </c>
-      <c r="D25" s="186">
+      <c r="D25" s="157">
         <f>SUM(C25:$C$31)</f>
         <v>10000</v>
       </c>
-      <c r="E25" s="187">
+      <c r="E25" s="158">
         <v>9973</v>
       </c>
       <c r="F25" s="147">
@@ -6649,18 +6638,18 @@
       <c r="O25" s="148"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="152"/>
+      <c r="A26" s="173"/>
       <c r="B26" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="186">
-        <v>0</v>
-      </c>
-      <c r="D26" s="186">
+      <c r="C26" s="157">
+        <v>0</v>
+      </c>
+      <c r="D26" s="157">
         <f>SUM(C26:$C$31)</f>
         <v>5000</v>
       </c>
-      <c r="E26" s="187">
+      <c r="E26" s="158">
         <v>4886</v>
       </c>
       <c r="F26" s="147">
@@ -6681,18 +6670,18 @@
       <c r="O26" s="148"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="153"/>
+      <c r="A27" s="174"/>
       <c r="B27" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="186">
+      <c r="C27" s="157">
         <v>5000</v>
       </c>
-      <c r="D27" s="186">
+      <c r="D27" s="157">
         <f>SUM(C27:$C$31)</f>
         <v>5000</v>
       </c>
-      <c r="E27" s="187">
+      <c r="E27" s="158">
         <v>4832</v>
       </c>
       <c r="F27" s="147">
@@ -7003,19 +6992,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="185" t="s">
+      <c r="B1" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="184" t="s">
+      <c r="C1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="188" t="s">
+      <c r="D1" s="159" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="189" t="s">
+      <c r="E1" s="160" t="s">
         <v>123</v>
       </c>
       <c r="F1" s="151" t="s">
@@ -7077,20 +7066,20 @@
       <c r="T3" s="121"/>
     </row>
     <row r="4" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163">
+      <c r="A4" s="172">
         <v>2025</v>
       </c>
       <c r="B4" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="186">
+      <c r="C4" s="157">
         <v>17500</v>
       </c>
-      <c r="D4" s="186">
+      <c r="D4" s="157">
         <f>SUM(C4:$C$31)</f>
         <v>96000</v>
       </c>
-      <c r="E4" s="186">
+      <c r="E4" s="157">
         <v>98137</v>
       </c>
       <c r="F4" s="147">
@@ -7114,18 +7103,18 @@
       <c r="R4" s="148"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="152"/>
+      <c r="A5" s="173"/>
       <c r="B5" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="186">
+      <c r="C5" s="157">
         <v>15000</v>
       </c>
-      <c r="D5" s="186">
+      <c r="D5" s="157">
         <f>SUM(C5:$C$31)</f>
         <v>78500</v>
       </c>
-      <c r="E5" s="186">
+      <c r="E5" s="157">
         <v>80437</v>
       </c>
       <c r="F5" s="147">
@@ -7149,18 +7138,18 @@
       <c r="R5" s="148"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="152"/>
+      <c r="A6" s="173"/>
       <c r="B6" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="186">
+      <c r="C6" s="157">
         <v>12500</v>
       </c>
-      <c r="D6" s="186">
+      <c r="D6" s="157">
         <f>SUM(C6:$C$31)</f>
         <v>63500</v>
       </c>
-      <c r="E6" s="186">
+      <c r="E6" s="157">
         <v>64804</v>
       </c>
       <c r="F6" s="147">
@@ -7184,18 +7173,18 @@
       <c r="R6" s="148"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="152"/>
+      <c r="A7" s="173"/>
       <c r="B7" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="186">
+      <c r="C7" s="157">
         <v>10000</v>
       </c>
-      <c r="D7" s="186">
+      <c r="D7" s="157">
         <f>SUM(C7:$C$31)</f>
         <v>51000</v>
       </c>
-      <c r="E7" s="186">
+      <c r="E7" s="157">
         <v>53018</v>
       </c>
       <c r="F7" s="147">
@@ -7219,18 +7208,18 @@
       <c r="R7" s="148"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="152"/>
+      <c r="A8" s="173"/>
       <c r="B8" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="186">
+      <c r="C8" s="157">
         <v>7500</v>
       </c>
-      <c r="D8" s="186">
+      <c r="D8" s="157">
         <f>SUM(C8:$C$31)</f>
         <v>41000</v>
       </c>
-      <c r="E8" s="186">
+      <c r="E8" s="157">
         <v>42016</v>
       </c>
       <c r="F8" s="147">
@@ -7254,18 +7243,18 @@
       <c r="R8" s="148"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="152"/>
+      <c r="A9" s="173"/>
       <c r="B9" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="186">
+      <c r="C9" s="157">
         <v>5000</v>
       </c>
-      <c r="D9" s="186">
+      <c r="D9" s="157">
         <f>SUM(C9:$C$31)</f>
         <v>33500</v>
       </c>
-      <c r="E9" s="186">
+      <c r="E9" s="157">
         <v>34413</v>
       </c>
       <c r="F9" s="147">
@@ -7289,18 +7278,18 @@
       <c r="R9" s="148"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="152"/>
+      <c r="A10" s="173"/>
       <c r="B10" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="186">
+      <c r="C10" s="157">
         <v>5000</v>
       </c>
-      <c r="D10" s="186">
+      <c r="D10" s="157">
         <f>SUM(C10:$C$31)</f>
         <v>28500</v>
       </c>
-      <c r="E10" s="186">
+      <c r="E10" s="157">
         <v>29874</v>
       </c>
       <c r="F10" s="147">
@@ -7324,18 +7313,18 @@
       <c r="R10" s="148"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="152"/>
+      <c r="A11" s="173"/>
       <c r="B11" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="186">
+      <c r="C11" s="157">
         <v>5000</v>
       </c>
-      <c r="D11" s="186">
+      <c r="D11" s="157">
         <f>SUM(C11:$C$31)</f>
         <v>23500</v>
       </c>
-      <c r="E11" s="186">
+      <c r="E11" s="157">
         <v>24301</v>
       </c>
       <c r="F11" s="147">
@@ -7359,18 +7348,18 @@
       <c r="R11" s="148"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="152"/>
+      <c r="A12" s="173"/>
       <c r="B12" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="186">
+      <c r="C12" s="157">
         <v>5000</v>
       </c>
-      <c r="D12" s="186">
+      <c r="D12" s="157">
         <f>SUM(C12:$C$31)</f>
         <v>18500</v>
       </c>
-      <c r="E12" s="186">
+      <c r="E12" s="157">
         <v>18790</v>
       </c>
       <c r="F12" s="147">
@@ -7394,18 +7383,18 @@
       <c r="R12" s="148"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="152"/>
+      <c r="A13" s="173"/>
       <c r="B13" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="186">
+      <c r="C13" s="157">
         <v>5000</v>
       </c>
-      <c r="D13" s="186">
+      <c r="D13" s="157">
         <f>SUM(C13:$C$31)</f>
         <v>13500</v>
       </c>
-      <c r="E13" s="186">
+      <c r="E13" s="157">
         <v>13490</v>
       </c>
       <c r="F13" s="147">
@@ -7429,18 +7418,18 @@
       <c r="R13" s="148"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="152"/>
+      <c r="A14" s="173"/>
       <c r="B14" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="186">
+      <c r="C14" s="157">
         <v>5000</v>
       </c>
-      <c r="D14" s="186">
+      <c r="D14" s="157">
         <f>SUM(C14:$C$31)</f>
         <v>8500</v>
       </c>
-      <c r="E14" s="186">
+      <c r="E14" s="157">
         <v>8449</v>
       </c>
       <c r="F14" s="147">
@@ -7464,18 +7453,18 @@
       <c r="R14" s="148"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="153"/>
+      <c r="A15" s="174"/>
       <c r="B15" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="186">
+      <c r="C15" s="157">
         <v>3500</v>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="157">
         <f>SUM(C15:$C$31)</f>
         <v>3500</v>
       </c>
-      <c r="E15" s="186">
+      <c r="E15" s="157">
         <v>3459</v>
       </c>
       <c r="F15" s="147">
@@ -7765,16 +7754,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="185" t="s">
+      <c r="B1" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="184" t="s">
+      <c r="C1" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="183" t="s">
+      <c r="D1" s="154" t="s">
         <v>46</v>
       </c>
       <c r="E1" s="151" t="s">
@@ -7797,7 +7786,7 @@
       <c r="F3" s="148"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="163">
+      <c r="A4" s="172">
         <v>2025</v>
       </c>
       <c r="B4" s="114" t="s">
@@ -7816,7 +7805,7 @@
       <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="152"/>
+      <c r="A5" s="173"/>
       <c r="B5" s="114" t="s">
         <v>36</v>
       </c>
@@ -7833,7 +7822,7 @@
       <c r="F5" s="148"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="152"/>
+      <c r="A6" s="173"/>
       <c r="B6" s="114" t="s">
         <v>37</v>
       </c>
@@ -7851,7 +7840,7 @@
       <c r="I6" s="115"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="152"/>
+      <c r="A7" s="173"/>
       <c r="B7" s="114" t="s">
         <v>38</v>
       </c>
@@ -7868,7 +7857,7 @@
       <c r="F7" s="148"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="152"/>
+      <c r="A8" s="173"/>
       <c r="B8" s="114" t="s">
         <v>39</v>
       </c>
@@ -7885,7 +7874,7 @@
       <c r="F8" s="148"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="152"/>
+      <c r="A9" s="173"/>
       <c r="B9" s="114" t="s">
         <v>40</v>
       </c>
@@ -7902,7 +7891,7 @@
       <c r="F9" s="148"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="152"/>
+      <c r="A10" s="173"/>
       <c r="B10" s="114" t="s">
         <v>41</v>
       </c>
@@ -7919,7 +7908,7 @@
       <c r="F10" s="148"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="152"/>
+      <c r="A11" s="173"/>
       <c r="B11" s="114" t="s">
         <v>8</v>
       </c>
@@ -7936,7 +7925,7 @@
       <c r="F11" s="148"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="152"/>
+      <c r="A12" s="173"/>
       <c r="B12" s="58" t="s">
         <v>42</v>
       </c>
@@ -7953,7 +7942,7 @@
       <c r="F12" s="148"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="152"/>
+      <c r="A13" s="173"/>
       <c r="B13" s="114" t="s">
         <v>43</v>
       </c>
@@ -7970,7 +7959,7 @@
       <c r="F13" s="148"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="152"/>
+      <c r="A14" s="173"/>
       <c r="B14" s="58" t="s">
         <v>44</v>
       </c>
@@ -7987,7 +7976,7 @@
       <c r="F14" s="148"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="153"/>
+      <c r="A15" s="174"/>
       <c r="B15" s="114" t="s">
         <v>34</v>
       </c>
@@ -8046,7 +8035,7 @@
     <col min="4" max="4" width="9.88671875" style="123" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.6640625" style="123" customWidth="1"/>
     <col min="6" max="6" width="9" style="123" customWidth="1"/>
-    <col min="7" max="7" width="6.44140625" style="123" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="123" customWidth="1"/>
     <col min="8" max="8" width="8.44140625" style="123" customWidth="1"/>
     <col min="9" max="9" width="12" style="123" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.77734375" style="123" customWidth="1"/>
@@ -8063,42 +8052,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="174"/>
-      <c r="B1" s="167" t="s">
+      <c r="A1" s="185"/>
+      <c r="B1" s="178" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="167" t="s">
+      <c r="C1" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="169" t="s">
+      <c r="D1" s="180" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="169" t="s">
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="169" t="s">
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="173"/>
-      <c r="P1" s="169" t="s">
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="184"/>
+      <c r="P1" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="171"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="182"/>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="168"/>
-      <c r="B2" s="168"/>
-      <c r="C2" s="168"/>
+      <c r="A2" s="179"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
       <c r="D2" s="133" t="s">
         <v>50</v>
       </c>
@@ -8149,7 +8138,7 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="172" t="s">
+      <c r="A3" s="183" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="135" t="s">
@@ -8169,7 +8158,7 @@
         <f>ROUND(E3/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="164">
+      <c r="G3" s="175">
         <f>SUM(F3:F12)</f>
         <v>48.04</v>
       </c>
@@ -8184,7 +8173,7 @@
         <f>ROUND(I3/I21*100, 2)</f>
         <v>21.73</v>
       </c>
-      <c r="K3" s="164">
+      <c r="K3" s="175">
         <f>SUM(J3:J12)</f>
         <v>91.960000000000008</v>
       </c>
@@ -8199,7 +8188,7 @@
         <f>ROUND(M3/M21*100, 2)</f>
         <v>33.96</v>
       </c>
-      <c r="O3" s="164">
+      <c r="O3" s="175">
         <f>SUM(N3:N12)</f>
         <v>87.51</v>
       </c>
@@ -8215,13 +8204,13 @@
         <f>ROUND(Q3/Q21*100, 2)</f>
         <v>15.57</v>
       </c>
-      <c r="S3" s="164">
+      <c r="S3" s="175">
         <f>SUM(R3:R12)</f>
         <v>72.819999999999993</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="165"/>
+      <c r="A4" s="177"/>
       <c r="B4" s="135" t="s">
         <v>54</v>
       </c>
@@ -8239,7 +8228,7 @@
         <f>ROUND(E4/E21*100, 2)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="G4" s="165"/>
+      <c r="G4" s="177"/>
       <c r="H4" s="137">
         <v>0</v>
       </c>
@@ -8251,7 +8240,7 @@
         <f>ROUND(I4/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="165"/>
+      <c r="K4" s="177"/>
       <c r="L4" s="137">
         <v>1</v>
       </c>
@@ -8263,7 +8252,7 @@
         <f>ROUND(M4/M21*100, 2)</f>
         <v>15.68</v>
       </c>
-      <c r="O4" s="165"/>
+      <c r="O4" s="177"/>
       <c r="P4" s="137">
         <f t="shared" si="3"/>
         <v>2</v>
@@ -8276,11 +8265,11 @@
         <f>ROUND(Q4/Q21*100, 2)</f>
         <v>7.18</v>
       </c>
-      <c r="S4" s="165"/>
+      <c r="S4" s="177"/>
       <c r="U4" s="82"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="165"/>
+      <c r="A5" s="177"/>
       <c r="B5" s="135" t="s">
         <v>55</v>
       </c>
@@ -8298,7 +8287,7 @@
         <f>ROUND(E5/E21*100, 2)</f>
         <v>3.99</v>
       </c>
-      <c r="G5" s="165"/>
+      <c r="G5" s="177"/>
       <c r="H5" s="137">
         <v>1</v>
       </c>
@@ -8310,7 +8299,7 @@
         <f>ROUND(I5/I21*100, 2)</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="K5" s="165"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="137">
         <v>1</v>
       </c>
@@ -8322,7 +8311,7 @@
         <f>ROUND(M5/M21*100, 2)</f>
         <v>7.18</v>
       </c>
-      <c r="O5" s="165"/>
+      <c r="O5" s="177"/>
       <c r="P5" s="137">
         <f t="shared" si="3"/>
         <v>3</v>
@@ -8335,11 +8324,11 @@
         <f>ROUND(Q5/Q21*100, 2)</f>
         <v>4.9400000000000004</v>
       </c>
-      <c r="S5" s="165"/>
+      <c r="S5" s="177"/>
       <c r="U5" s="82"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="165"/>
+      <c r="A6" s="177"/>
       <c r="B6" s="135" t="s">
         <v>56</v>
       </c>
@@ -8357,7 +8346,7 @@
         <f>ROUND(E6/E21*100, 2)</f>
         <v>1.99</v>
       </c>
-      <c r="G6" s="165"/>
+      <c r="G6" s="177"/>
       <c r="H6" s="137">
         <v>0</v>
       </c>
@@ -8369,7 +8358,7 @@
         <f>ROUND(I6/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="165"/>
+      <c r="K6" s="177"/>
       <c r="L6" s="137">
         <v>0</v>
       </c>
@@ -8381,7 +8370,7 @@
         <f>ROUND(M6/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="165"/>
+      <c r="O6" s="177"/>
       <c r="P6" s="137">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -8394,14 +8383,14 @@
         <f>ROUND(Q6/Q21*100, 2)</f>
         <v>0.82</v>
       </c>
-      <c r="S6" s="165"/>
+      <c r="S6" s="177"/>
       <c r="U6" s="141"/>
       <c r="V6" s="142"/>
       <c r="W6" s="142"/>
       <c r="X6" s="142"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="165"/>
+      <c r="A7" s="177"/>
       <c r="B7" s="135" t="s">
         <v>57</v>
       </c>
@@ -8419,7 +8408,7 @@
         <f>ROUND(E7/E21*100, 2)</f>
         <v>10.15</v>
       </c>
-      <c r="G7" s="165"/>
+      <c r="G7" s="177"/>
       <c r="H7" s="137">
         <v>0</v>
       </c>
@@ -8431,7 +8420,7 @@
         <f>ROUND(I7/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="165"/>
+      <c r="K7" s="177"/>
       <c r="L7" s="137">
         <v>0</v>
       </c>
@@ -8443,7 +8432,7 @@
         <f>ROUND(M7/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="165"/>
+      <c r="O7" s="177"/>
       <c r="P7" s="137">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -8456,14 +8445,14 @@
         <f>ROUND(Q7/Q21*100, 2)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="S7" s="165"/>
+      <c r="S7" s="177"/>
       <c r="U7" s="143"/>
       <c r="V7" s="142"/>
       <c r="W7" s="142"/>
       <c r="X7" s="142"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="165"/>
+      <c r="A8" s="177"/>
       <c r="B8" s="135" t="s">
         <v>59</v>
       </c>
@@ -8481,7 +8470,7 @@
         <f>ROUND(E8/E21*100, 2)</f>
         <v>6.53</v>
       </c>
-      <c r="G8" s="165"/>
+      <c r="G8" s="177"/>
       <c r="H8" s="137">
         <v>0</v>
       </c>
@@ -8493,7 +8482,7 @@
         <f>ROUND(I8/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="165"/>
+      <c r="K8" s="177"/>
       <c r="L8" s="137">
         <v>0</v>
       </c>
@@ -8505,7 +8494,7 @@
         <f>ROUND(M8/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="165"/>
+      <c r="O8" s="177"/>
       <c r="P8" s="137">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -8518,14 +8507,14 @@
         <f>ROUND(Q8/Q21*100, 2)</f>
         <v>2.69</v>
       </c>
-      <c r="S8" s="165"/>
+      <c r="S8" s="177"/>
       <c r="U8" s="143"/>
       <c r="V8" s="142"/>
       <c r="W8" s="142"/>
       <c r="X8" s="142"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="165"/>
+      <c r="A9" s="177"/>
       <c r="B9" s="135" t="s">
         <v>60</v>
       </c>
@@ -8543,7 +8532,7 @@
         <f>ROUND(E9/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="165"/>
+      <c r="G9" s="177"/>
       <c r="H9" s="137">
         <v>1</v>
       </c>
@@ -8555,7 +8544,7 @@
         <f>ROUND(I9/I21*100, 2)</f>
         <v>18.809999999999999</v>
       </c>
-      <c r="K9" s="165"/>
+      <c r="K9" s="177"/>
       <c r="L9" s="137">
         <v>0</v>
       </c>
@@ -8567,7 +8556,7 @@
         <f>ROUND(M9/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="165"/>
+      <c r="O9" s="177"/>
       <c r="P9" s="137">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -8580,10 +8569,10 @@
         <f>ROUND(Q9/Q21*100, 2)</f>
         <v>6.74</v>
       </c>
-      <c r="S9" s="165"/>
+      <c r="S9" s="177"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="165"/>
+      <c r="A10" s="177"/>
       <c r="B10" s="135" t="s">
         <v>61</v>
       </c>
@@ -8601,7 +8590,7 @@
         <f>ROUND(E10/E21*100, 2)</f>
         <v>16.68</v>
       </c>
-      <c r="G10" s="165"/>
+      <c r="G10" s="177"/>
       <c r="H10" s="137">
         <v>1</v>
       </c>
@@ -8613,7 +8602,7 @@
         <f>ROUND(I10/I21*100, 2)</f>
         <v>19.23</v>
       </c>
-      <c r="K10" s="165"/>
+      <c r="K10" s="177"/>
       <c r="L10" s="137">
         <v>0</v>
       </c>
@@ -8625,7 +8614,7 @@
         <f>ROUND(M10/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="165"/>
+      <c r="O10" s="177"/>
       <c r="P10" s="137">
         <f t="shared" si="3"/>
         <v>2</v>
@@ -8638,10 +8627,10 @@
         <f>ROUND(Q10/Q21*100, 2)</f>
         <v>13.77</v>
       </c>
-      <c r="S10" s="165"/>
+      <c r="S10" s="177"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="165"/>
+      <c r="A11" s="177"/>
       <c r="B11" s="135" t="s">
         <v>62</v>
       </c>
@@ -8659,7 +8648,7 @@
         <f>ROUND(E11/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="165"/>
+      <c r="G11" s="177"/>
       <c r="H11" s="137">
         <v>2</v>
       </c>
@@ -8671,7 +8660,7 @@
         <f>ROUND(I11/I21*100, 2)</f>
         <v>27.59</v>
       </c>
-      <c r="K11" s="165"/>
+      <c r="K11" s="177"/>
       <c r="L11" s="137">
         <v>1</v>
       </c>
@@ -8683,7 +8672,7 @@
         <f>ROUND(M11/M21*100, 2)</f>
         <v>21.55</v>
       </c>
-      <c r="O11" s="165"/>
+      <c r="O11" s="177"/>
       <c r="P11" s="137">
         <f t="shared" si="3"/>
         <v>3</v>
@@ -8696,10 +8685,10 @@
         <f>ROUND(Q11/Q21*100, 2)</f>
         <v>14.82</v>
       </c>
-      <c r="S11" s="165"/>
+      <c r="S11" s="177"/>
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="175"/>
+      <c r="A12" s="186"/>
       <c r="B12" s="139" t="s">
         <v>68</v>
       </c>
@@ -8717,7 +8706,7 @@
         <f>ROUND(E12/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="166"/>
+      <c r="G12" s="176"/>
       <c r="H12" s="140">
         <v>0</v>
       </c>
@@ -8729,7 +8718,7 @@
         <f>ROUND(I12/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="166"/>
+      <c r="K12" s="176"/>
       <c r="L12" s="140">
         <v>1</v>
       </c>
@@ -8741,7 +8730,7 @@
         <f>ROUND(M12/M21*100, 2)</f>
         <v>9.14</v>
       </c>
-      <c r="O12" s="166"/>
+      <c r="O12" s="176"/>
       <c r="P12" s="140">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -8754,10 +8743,10 @@
         <f>ROUND(Q12/Q21*100, 2)</f>
         <v>2.1</v>
       </c>
-      <c r="S12" s="166"/>
+      <c r="S12" s="176"/>
     </row>
     <row r="13" spans="1:24" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="172" t="s">
+      <c r="A13" s="183" t="s">
         <v>69</v>
       </c>
       <c r="B13" s="135" t="s">
@@ -8777,7 +8766,7 @@
         <f>ROUND(E13/E21*100, 2)</f>
         <v>2.25</v>
       </c>
-      <c r="G13" s="164">
+      <c r="G13" s="175">
         <f>SUM(F13:F17)</f>
         <v>15.67</v>
       </c>
@@ -8792,7 +8781,7 @@
         <f>ROUND(I13/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="164">
+      <c r="K13" s="175">
         <f>SUM(J13:J17)</f>
         <v>7.73</v>
       </c>
@@ -8807,7 +8796,7 @@
         <f>ROUND(M13/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="164">
+      <c r="O13" s="175">
         <f>SUM(N13:N17)</f>
         <v>5.94</v>
       </c>
@@ -8823,13 +8812,13 @@
         <f>ROUND(Q13/Q21*100, 2)</f>
         <v>0.93</v>
       </c>
-      <c r="S13" s="164">
+      <c r="S13" s="175">
         <f>SUM(R13:R17)</f>
         <v>10.6</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="165"/>
+      <c r="A14" s="177"/>
       <c r="B14" s="135" t="s">
         <v>71</v>
       </c>
@@ -8847,7 +8836,7 @@
         <f>ROUND(E14/E21*100, 2)</f>
         <v>6.6</v>
       </c>
-      <c r="G14" s="165"/>
+      <c r="G14" s="177"/>
       <c r="H14" s="137">
         <v>1</v>
       </c>
@@ -8859,7 +8848,7 @@
         <f>ROUND(I14/I21*100, 2)</f>
         <v>3.8</v>
       </c>
-      <c r="K14" s="165"/>
+      <c r="K14" s="177"/>
       <c r="L14" s="137">
         <v>1</v>
       </c>
@@ -8871,7 +8860,7 @@
         <f>ROUND(M14/M21*100, 2)</f>
         <v>5.94</v>
       </c>
-      <c r="O14" s="165"/>
+      <c r="O14" s="177"/>
       <c r="P14" s="137">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -8884,10 +8873,10 @@
         <f>ROUND(Q14/Q21*100, 2)</f>
         <v>5.45</v>
       </c>
-      <c r="S14" s="165"/>
+      <c r="S14" s="177"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="165"/>
+      <c r="A15" s="177"/>
       <c r="B15" s="135" t="s">
         <v>72</v>
       </c>
@@ -8905,7 +8894,7 @@
         <f>ROUND(E15/E21*100, 2)</f>
         <v>6.82</v>
       </c>
-      <c r="G15" s="165"/>
+      <c r="G15" s="177"/>
       <c r="H15" s="137">
         <v>1</v>
       </c>
@@ -8917,7 +8906,7 @@
         <f>ROUND(I15/I21*100, 2)</f>
         <v>3.93</v>
       </c>
-      <c r="K15" s="165"/>
+      <c r="K15" s="177"/>
       <c r="L15" s="137">
         <v>0</v>
       </c>
@@ -8929,7 +8918,7 @@
         <f>ROUND(M15/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O15" s="165"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="137">
         <f t="shared" si="3"/>
         <v>3</v>
@@ -8942,10 +8931,10 @@
         <f>ROUND(Q15/Q21*100, 2)</f>
         <v>4.22</v>
       </c>
-      <c r="S15" s="165"/>
+      <c r="S15" s="177"/>
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="165"/>
+      <c r="A16" s="177"/>
       <c r="B16" s="135" t="s">
         <v>73</v>
       </c>
@@ -8963,7 +8952,7 @@
         <f>ROUND(E16/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="165"/>
+      <c r="G16" s="177"/>
       <c r="H16" s="137">
         <v>0</v>
       </c>
@@ -8975,7 +8964,7 @@
         <f>ROUND(I16/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="165"/>
+      <c r="K16" s="177"/>
       <c r="L16" s="137">
         <v>0</v>
       </c>
@@ -8987,7 +8976,7 @@
         <f>ROUND(M16/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="165"/>
+      <c r="O16" s="177"/>
       <c r="P16" s="137">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -9000,10 +8989,10 @@
         <f>ROUND(Q16/Q21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="165"/>
+      <c r="S16" s="177"/>
     </row>
     <row r="17" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="175"/>
+      <c r="A17" s="186"/>
       <c r="B17" s="139" t="s">
         <v>74</v>
       </c>
@@ -9021,7 +9010,7 @@
         <f>ROUND(E17/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="166"/>
+      <c r="G17" s="176"/>
       <c r="H17" s="140">
         <v>0</v>
       </c>
@@ -9033,7 +9022,7 @@
         <f>ROUND(I17/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="166"/>
+      <c r="K17" s="176"/>
       <c r="L17" s="140">
         <v>0</v>
       </c>
@@ -9045,7 +9034,7 @@
         <f>ROUND(M17/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="166"/>
+      <c r="O17" s="176"/>
       <c r="P17" s="140">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -9058,10 +9047,10 @@
         <f>ROUND(Q17/Q21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="166"/>
+      <c r="S17" s="176"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="172" t="s">
+      <c r="A18" s="183" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="135" t="s">
@@ -9081,7 +9070,7 @@
         <f>ROUND(E18/E21*100, 2)</f>
         <v>36.26</v>
       </c>
-      <c r="G18" s="164">
+      <c r="G18" s="175">
         <f>SUM(F18:F19)</f>
         <v>36.26</v>
       </c>
@@ -9096,7 +9085,7 @@
         <f>ROUND(I18/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="164">
+      <c r="K18" s="175">
         <f>SUM(J18:J19)</f>
         <v>0</v>
       </c>
@@ -9111,7 +9100,7 @@
         <f>ROUND(M18/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="164">
+      <c r="O18" s="175">
         <f>SUM(N18:N19)</f>
         <v>0</v>
       </c>
@@ -9127,13 +9116,13 @@
         <f>ROUND(Q18/Q21*100, 2)</f>
         <v>14.97</v>
       </c>
-      <c r="S18" s="164">
+      <c r="S18" s="175">
         <f>SUM(R18:R19)</f>
         <v>14.97</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="175"/>
+      <c r="A19" s="186"/>
       <c r="B19" s="139" t="s">
         <v>77</v>
       </c>
@@ -9151,7 +9140,7 @@
         <f>ROUND(E19/E21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="166"/>
+      <c r="G19" s="176"/>
       <c r="H19" s="140">
         <v>0</v>
       </c>
@@ -9163,7 +9152,7 @@
         <f>ROUND(I19/I21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="166"/>
+      <c r="K19" s="176"/>
       <c r="L19" s="140">
         <v>0</v>
       </c>
@@ -9175,7 +9164,7 @@
         <f>ROUND(M19/M21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="166"/>
+      <c r="O19" s="176"/>
       <c r="P19" s="140">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -9188,10 +9177,10 @@
         <f>ROUND(Q19/Q21*100, 2)</f>
         <v>0</v>
       </c>
-      <c r="S19" s="166"/>
+      <c r="S19" s="176"/>
     </row>
     <row r="20" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="172" t="s">
+      <c r="A20" s="183" t="s">
         <v>78</v>
       </c>
       <c r="B20" s="139" t="s">
@@ -9332,20 +9321,20 @@
       <c r="A1" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="176">
+      <c r="B1" s="187">
         <v>2025</v>
       </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="177"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="188"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="43" t="s">
@@ -9561,7 +9550,7 @@
         <v>8637</v>
       </c>
       <c r="M6" s="113">
-        <v>8712</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9614,7 +9603,7 @@
       </c>
       <c r="M7" s="103">
         <f t="shared" si="0"/>
-        <v>402904</v>
+        <v>414192</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9761,7 +9750,7 @@
       </c>
       <c r="M10" s="104">
         <f t="shared" si="2"/>
-        <v>403264</v>
+        <v>414552</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -9769,20 +9758,20 @@
       <c r="A13" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="176">
+      <c r="B13" s="187">
         <v>2024</v>
       </c>
-      <c r="C13" s="158"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="158"/>
-      <c r="I13" s="158"/>
-      <c r="J13" s="158"/>
-      <c r="K13" s="158"/>
-      <c r="L13" s="158"/>
-      <c r="M13" s="177"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="164"/>
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
+      <c r="G13" s="164"/>
+      <c r="H13" s="164"/>
+      <c r="I13" s="164"/>
+      <c r="J13" s="164"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="164"/>
+      <c r="M13" s="188"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="43" t="s">
@@ -10586,8 +10575,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="178"/>
-      <c r="B1" s="155"/>
+      <c r="A1" s="189"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="64" t="s">
         <v>80</v>
       </c>
